--- a/database/event/5729/event_5729_evp_summary.xlsx
+++ b/database/event/5729/event_5729_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.589700000000001</v>
+        <v>11.2938</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0165</v>
+        <v>4.7302</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4527</v>
+        <v>4.0555</v>
       </c>
       <c r="E2" t="n">
-        <v>9.589700000000001</v>
+        <v>11.2938</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0057</v>
+        <v>4.7098</v>
       </c>
       <c r="G2" t="n">
         <v>6.5839</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0057</v>
+        <v>5.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0338</v>
+        <v>5.1678</v>
       </c>
       <c r="J2" t="n">
         <v>7.488</v>
@@ -529,7 +529,7 @@
         <v>249</v>
       </c>
       <c r="M2" t="n">
-        <v>10.5218</v>
+        <v>12.6558</v>
       </c>
       <c r="N2" t="n">
         <v>374</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0603</v>
+        <v>7.8064</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9571</v>
+        <v>3.2696</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4308</v>
+        <v>2.6662</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0603</v>
+        <v>7.8064</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1755</v>
+        <v>4.9216</v>
       </c>
       <c r="G3" t="n">
         <v>2.8848</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2442</v>
+        <v>5.4141</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2639</v>
+        <v>5.4596</v>
       </c>
       <c r="J3" t="n">
         <v>2.8848</v>
@@ -575,7 +575,7 @@
         <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>7.1487</v>
+        <v>8.3444</v>
       </c>
       <c r="N3" t="n">
         <v>286</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9599</v>
+        <v>7.5799</v>
       </c>
       <c r="C4" t="n">
-        <v>2.915</v>
+        <v>3.1747</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3903</v>
+        <v>2.5759</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9599</v>
+        <v>7.5799</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5501</v>
+        <v>4.477</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4098</v>
+        <v>3.103</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5501</v>
+        <v>4.7168</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5645</v>
+        <v>4.7965</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4098</v>
+        <v>3.103</v>
       </c>
       <c r="K4" t="n">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="L4" t="n">
-        <v>249</v>
+        <v>133</v>
       </c>
       <c r="M4" t="n">
-        <v>6.974299999999999</v>
+        <v>7.8995</v>
       </c>
       <c r="N4" t="n">
-        <v>374</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.5631</v>
+        <v>7.2339</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7488</v>
+        <v>3.0298</v>
       </c>
       <c r="D5" t="n">
-        <v>2.23</v>
+        <v>2.4381</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5631</v>
+        <v>7.2339</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4601</v>
+        <v>1.8241</v>
       </c>
       <c r="G5" t="n">
-        <v>3.103</v>
+        <v>5.4098</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4601</v>
+        <v>1.8241</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4924</v>
+        <v>1.8549</v>
       </c>
       <c r="J5" t="n">
-        <v>3.103</v>
+        <v>5.4098</v>
       </c>
       <c r="K5" t="n">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="L5" t="n">
-        <v>133</v>
+        <v>249</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5954</v>
+        <v>7.264699999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>341</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.3316</v>
+        <v>7.1402</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6519</v>
+        <v>2.9905</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1365</v>
+        <v>2.4007</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3316</v>
+        <v>7.1402</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4198</v>
+        <v>2.9027</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9118</v>
+        <v>4.2375</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6271</v>
+        <v>2.9027</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7139</v>
+        <v>2.9518</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9118</v>
+        <v>4.2375</v>
       </c>
       <c r="K6" t="n">
-        <v>232</v>
+        <v>125</v>
       </c>
       <c r="L6" t="n">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="M6" t="n">
-        <v>6.6257</v>
+        <v>7.189299999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.206</v>
+        <v>7.0332</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5993</v>
+        <v>2.9457</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0857</v>
+        <v>2.3581</v>
       </c>
       <c r="E7" t="n">
-        <v>6.206</v>
+        <v>7.0332</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4263</v>
+        <v>5.2535</v>
       </c>
       <c r="G7" t="n">
         <v>1.7797</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6373</v>
+        <v>5.9344</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6806</v>
+        <v>6.0347</v>
       </c>
       <c r="J7" t="n">
         <v>1.7797</v>
@@ -759,7 +759,7 @@
         <v>133</v>
       </c>
       <c r="M7" t="n">
-        <v>6.4603</v>
+        <v>7.8144</v>
       </c>
       <c r="N7" t="n">
         <v>341</v>
@@ -768,323 +768,323 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.1807</v>
+        <v>6.9845</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5887</v>
+        <v>2.9253</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0755</v>
+        <v>2.3387</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1807</v>
+        <v>6.9845</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7643</v>
+        <v>5.0727</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4164</v>
+        <v>1.9118</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7643</v>
+        <v>5.6508</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7772</v>
+        <v>5.8435</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4164</v>
+        <v>1.9118</v>
       </c>
       <c r="K8" t="n">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="L8" t="n">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="M8" t="n">
-        <v>6.1936</v>
+        <v>7.7553</v>
       </c>
       <c r="N8" t="n">
-        <v>389</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.1572</v>
+        <v>6.5801</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5788</v>
+        <v>2.756</v>
       </c>
       <c r="D9" t="n">
-        <v>2.066</v>
+        <v>2.1776</v>
       </c>
       <c r="E9" t="n">
-        <v>6.1572</v>
+        <v>6.5801</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9197</v>
+        <v>3.1637</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2375</v>
+        <v>3.4164</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9197</v>
+        <v>3.1637</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9376</v>
+        <v>3.1903</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2375</v>
+        <v>3.4164</v>
       </c>
       <c r="K9" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="L9" t="n">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="M9" t="n">
-        <v>6.1751</v>
+        <v>6.6067</v>
       </c>
       <c r="N9" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.056</v>
+        <v>6.4964</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5364</v>
+        <v>2.7209</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0251</v>
+        <v>2.1443</v>
       </c>
       <c r="E10" t="n">
-        <v>6.056</v>
+        <v>6.4964</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0602</v>
+        <v>3.9424</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9958</v>
+        <v>2.5539</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0602</v>
+        <v>3.9424</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2909</v>
+        <v>3.1955</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9958</v>
+        <v>2.5539</v>
       </c>
       <c r="K10" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="L10" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2867</v>
+        <v>5.7494</v>
       </c>
       <c r="N10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.9841</v>
+        <v>6.4575</v>
       </c>
       <c r="C11" t="n">
-        <v>2.5063</v>
+        <v>2.7046</v>
       </c>
       <c r="D11" t="n">
-        <v>1.9961</v>
+        <v>2.1288</v>
       </c>
       <c r="E11" t="n">
-        <v>5.9841</v>
+        <v>6.4575</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7654</v>
+        <v>4.4617</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2187</v>
+        <v>1.9958</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7654</v>
+        <v>5.3899</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7736</v>
+        <v>4.3687</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2187</v>
+        <v>1.9958</v>
       </c>
       <c r="K11" t="n">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="L11" t="n">
-        <v>229</v>
+        <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>5.9923</v>
+        <v>6.3645</v>
       </c>
       <c r="N11" t="n">
-        <v>389</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.9312</v>
+        <v>5.9775</v>
       </c>
       <c r="C12" t="n">
-        <v>2.4842</v>
+        <v>2.5036</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9747</v>
+        <v>1.9375</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9312</v>
+        <v>5.9775</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3773</v>
+        <v>1.7588</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5539</v>
+        <v>4.2187</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3773</v>
+        <v>1.7588</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7374</v>
+        <v>1.7736</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5539</v>
+        <v>4.2187</v>
       </c>
       <c r="K12" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="L12" t="n">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2913</v>
+        <v>5.9923</v>
       </c>
       <c r="N12" t="n">
-        <v>246</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6357</v>
+        <v>5.8652</v>
       </c>
       <c r="C13" t="n">
-        <v>2.3604</v>
+        <v>2.4565</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8553</v>
+        <v>1.8928</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6357</v>
+        <v>5.8652</v>
       </c>
       <c r="F13" t="n">
-        <v>4.6123</v>
+        <v>4.336</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0234</v>
+        <v>1.5292</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9958</v>
+        <v>4.4958</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8598</v>
+        <v>4.6491</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0234</v>
+        <v>1.5292</v>
       </c>
       <c r="K13" t="n">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="L13" t="n">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8832</v>
+        <v>6.1783</v>
       </c>
       <c r="N13" t="n">
-        <v>246</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.5736</v>
+        <v>5.7836</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9156</v>
+        <v>2.4224</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4263</v>
+        <v>1.8603</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5736</v>
+        <v>5.7836</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0444</v>
+        <v>4.7602</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5292</v>
+        <v>1.0234</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0444</v>
+        <v>6.5909</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1015</v>
+        <v>5.3421</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5292</v>
+        <v>1.0234</v>
       </c>
       <c r="K14" t="n">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="L14" t="n">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6307</v>
+        <v>6.365500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>378</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.3925</v>
+        <v>4.4018</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8397</v>
+        <v>1.8436</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3531</v>
+        <v>1.3098</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3925</v>
+        <v>4.4018</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3102</v>
+        <v>4.3195</v>
       </c>
       <c r="G15" t="n">
         <v>0.0823</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7805</v>
+        <v>4.8178</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8748</v>
+        <v>3.9049</v>
       </c>
       <c r="J15" t="n">
         <v>0.0823</v>
@@ -1127,7 +1127,7 @@
         <v>76</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9571</v>
+        <v>3.9872</v>
       </c>
       <c r="N15" t="n">
         <v>279</v>
@@ -1136,829 +1136,829 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3876</v>
+        <v>4.1378</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4188</v>
+        <v>1.733</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9472</v>
+        <v>1.2046</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3876</v>
+        <v>4.1378</v>
       </c>
       <c r="F16" t="n">
-        <v>4.1683</v>
+        <v>3.8896</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.2482</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2097</v>
+        <v>3.8896</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4121</v>
+        <v>4.0222</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.2482</v>
       </c>
       <c r="K16" t="n">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="L16" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6314</v>
+        <v>4.2704</v>
       </c>
       <c r="N16" t="n">
-        <v>279</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3633</v>
+        <v>4.0474</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4087</v>
+        <v>1.6952</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9373</v>
+        <v>1.1686</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3633</v>
+        <v>4.0474</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4566</v>
+        <v>4.2382</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9067</v>
+        <v>-0.1908</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4566</v>
+        <v>4.4907</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9912</v>
+        <v>3.6398</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9067</v>
+        <v>-0.1908</v>
       </c>
       <c r="K17" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L17" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8979</v>
+        <v>3.449</v>
       </c>
       <c r="N17" t="n">
-        <v>279</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3503</v>
+        <v>4.0402</v>
       </c>
       <c r="C18" t="n">
-        <v>1.4032</v>
+        <v>1.6922</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9321</v>
+        <v>1.1657</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3503</v>
+        <v>4.0402</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1536</v>
+        <v>2.89</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1967</v>
+        <v>1.1502</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1536</v>
+        <v>2.89</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5561</v>
+        <v>2.9389</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1967</v>
+        <v>1.1502</v>
       </c>
       <c r="K18" t="n">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="L18" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7528</v>
+        <v>4.0891</v>
       </c>
       <c r="N18" t="n">
-        <v>246</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.3242</v>
+        <v>3.9898</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3923</v>
+        <v>1.6711</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9215</v>
+        <v>1.1456</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3242</v>
+        <v>3.9898</v>
       </c>
       <c r="F19" t="n">
-        <v>3.515</v>
+        <v>2.5664</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1908</v>
+        <v>1.4234</v>
       </c>
       <c r="H19" t="n">
-        <v>3.515</v>
+        <v>2.5664</v>
       </c>
       <c r="I19" t="n">
-        <v>2.849</v>
+        <v>2.6539</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1908</v>
+        <v>1.4234</v>
       </c>
       <c r="K19" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="L19" t="n">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6582</v>
+        <v>4.0773</v>
       </c>
       <c r="N19" t="n">
-        <v>256</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.2193</v>
+        <v>3.9348</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3483</v>
+        <v>1.648</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8792</v>
+        <v>1.1237</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2193</v>
+        <v>3.9348</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7959</v>
+        <v>3.7381</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4234</v>
+        <v>0.1967</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7959</v>
+        <v>3.7381</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8296</v>
+        <v>3.0298</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4234</v>
+        <v>0.1967</v>
       </c>
       <c r="K20" t="n">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="L20" t="n">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="M20" t="n">
-        <v>3.253</v>
+        <v>3.2265</v>
       </c>
       <c r="N20" t="n">
-        <v>348</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.1661</v>
+        <v>3.8196</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3261</v>
+        <v>1.5998</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8577</v>
+        <v>1.0778</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1661</v>
+        <v>3.8196</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0159</v>
+        <v>2.9129</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1502</v>
+        <v>0.9067</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0159</v>
+        <v>2.9129</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0347</v>
+        <v>2.361</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1502</v>
+        <v>0.9067</v>
       </c>
       <c r="K21" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="L21" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1849</v>
+        <v>3.2677</v>
       </c>
       <c r="N21" t="n">
-        <v>341</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.9857</v>
+        <v>3.5877</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2505</v>
+        <v>1.5026</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.9857</v>
+        <v>3.5877</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7375</v>
+        <v>0.7217</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2482</v>
+        <v>2.866</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7375</v>
+        <v>0.7217</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7888</v>
+        <v>0.7339</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2482</v>
+        <v>2.866</v>
       </c>
       <c r="K22" t="n">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="L22" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="M22" t="n">
-        <v>3.037</v>
+        <v>3.5999</v>
       </c>
       <c r="N22" t="n">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.8248</v>
+        <v>3.4708</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1831</v>
+        <v>1.4537</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7198</v>
+        <v>0.9389</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8248</v>
+        <v>3.4708</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9501</v>
+        <v>4.2515</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8747</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9501</v>
+        <v>4.5443</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9683</v>
+        <v>3.6833</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8747</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L23" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="M23" t="n">
-        <v>2.843</v>
+        <v>2.9026</v>
       </c>
       <c r="N23" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7927</v>
+        <v>3.3573</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1697</v>
+        <v>1.4061</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7068</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7927</v>
+        <v>3.3573</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6177</v>
+        <v>3.6606</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.825</v>
+        <v>-0.3033</v>
       </c>
       <c r="H24" t="n">
-        <v>3.6177</v>
+        <v>3.6606</v>
       </c>
       <c r="I24" t="n">
-        <v>3.6345</v>
+        <v>3.7854</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.825</v>
+        <v>-0.3033</v>
       </c>
       <c r="K24" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="L24" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8095</v>
+        <v>3.4821</v>
       </c>
       <c r="N24" t="n">
-        <v>286</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>h4rn</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7395</v>
+        <v>3.2535</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1474</v>
+        <v>1.3627</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6853</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>2.7395</v>
+        <v>3.2535</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1265</v>
+        <v>3.3012</v>
       </c>
       <c r="G25" t="n">
-        <v>2.866</v>
+        <v>-0.0477</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1265</v>
+        <v>3.3012</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1276</v>
+        <v>3.3012</v>
       </c>
       <c r="J25" t="n">
-        <v>2.866</v>
+        <v>-0.0477</v>
       </c>
       <c r="K25" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L25" t="n">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7384</v>
+        <v>3.2535</v>
       </c>
       <c r="N25" t="n">
-        <v>341</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>doto</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4654</v>
+        <v>3.2533</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0326</v>
+        <v>1.3626</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5746</v>
+        <v>0.8522</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4654</v>
+        <v>3.2533</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3455</v>
+        <v>4.0783</v>
       </c>
       <c r="G26" t="n">
-        <v>1.1199</v>
+        <v>-0.825</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3455</v>
+        <v>4.0918</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3517</v>
+        <v>4.1262</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1199</v>
+        <v>-0.825</v>
       </c>
       <c r="K26" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="L26" t="n">
-        <v>229</v>
+        <v>122</v>
       </c>
       <c r="M26" t="n">
-        <v>2.4716</v>
+        <v>3.3012</v>
       </c>
       <c r="N26" t="n">
-        <v>389</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rainwaker</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.4558</v>
+        <v>3.2435</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0286</v>
+        <v>1.3585</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5707</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4558</v>
+        <v>3.2435</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4558</v>
+        <v>2.3688</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.8747</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4558</v>
+        <v>2.3688</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4558</v>
+        <v>2.4088</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.8747</v>
       </c>
       <c r="K27" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M27" t="n">
-        <v>2.4558</v>
+        <v>3.2835</v>
       </c>
       <c r="N27" t="n">
-        <v>159</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>h4rn</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.366</v>
+        <v>3.2157</v>
       </c>
       <c r="C28" t="n">
-        <v>0.991</v>
+        <v>1.3468</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5344</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>2.366</v>
+        <v>3.2157</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4137</v>
+        <v>3.2157</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0477</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4137</v>
+        <v>3.2157</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4137</v>
+        <v>3.2157</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0477</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="L28" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.366</v>
+        <v>3.2157</v>
       </c>
       <c r="N28" t="n">
-        <v>306</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.3566</v>
+        <v>2.8577</v>
       </c>
       <c r="C29" t="n">
-        <v>0.987</v>
+        <v>1.1969</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.6946</v>
       </c>
       <c r="E29" t="n">
-        <v>2.3566</v>
+        <v>2.8577</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4111</v>
+        <v>2.3471</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9455</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4111</v>
+        <v>2.3471</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4243</v>
+        <v>2.3669</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9455</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="L29" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="M29" t="n">
-        <v>2.3698</v>
+        <v>2.8775</v>
       </c>
       <c r="N29" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.3467</v>
+        <v>2.8332</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9829</v>
+        <v>1.1866</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.6848</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3467</v>
+        <v>2.8332</v>
       </c>
       <c r="F30" t="n">
-        <v>2.3467</v>
+        <v>2.8332</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.3467</v>
+        <v>2.8332</v>
       </c>
       <c r="I30" t="n">
-        <v>2.3467</v>
+        <v>2.8332</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.3467</v>
+        <v>2.8332</v>
       </c>
       <c r="N30" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>doto</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.2674</v>
+        <v>2.7665</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9497</v>
+        <v>1.1587</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4946</v>
+        <v>0.6583</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2674</v>
+        <v>2.7665</v>
       </c>
       <c r="F31" t="n">
-        <v>2.2674</v>
+        <v>1.6466</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.1199</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2674</v>
+        <v>1.6466</v>
       </c>
       <c r="I31" t="n">
-        <v>2.2674</v>
+        <v>1.6605</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.1199</v>
       </c>
       <c r="K31" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="M31" t="n">
-        <v>2.2674</v>
+        <v>2.7804</v>
       </c>
       <c r="N31" t="n">
-        <v>152</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.2305</v>
+        <v>2.6053</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9342</v>
+        <v>1.0912</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4797</v>
+        <v>0.594</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2305</v>
+        <v>2.6053</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7199</v>
+        <v>2.6053</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5106000000000001</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7199</v>
+        <v>2.6053</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7279</v>
+        <v>2.6053</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5106000000000001</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="L32" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.2385</v>
+        <v>2.6053</v>
       </c>
       <c r="N32" t="n">
-        <v>286</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.1784</v>
+        <v>2.5558</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9124</v>
+        <v>1.0705</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4587</v>
+        <v>0.5743</v>
       </c>
       <c r="E33" t="n">
-        <v>2.1784</v>
+        <v>2.5558</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1784</v>
+        <v>2.5558</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1784</v>
+        <v>2.5558</v>
       </c>
       <c r="I33" t="n">
-        <v>2.1784</v>
+        <v>2.5558</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.1784</v>
+        <v>2.5558</v>
       </c>
       <c r="N33" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.0699</v>
+        <v>2.5213</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8669</v>
+        <v>1.056</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4148</v>
+        <v>0.5606</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0699</v>
+        <v>2.5213</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0699</v>
+        <v>2.5213</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.0699</v>
+        <v>2.5213</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0699</v>
+        <v>2.5213</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.0699</v>
+        <v>2.5213</v>
       </c>
       <c r="N34" t="n">
         <v>152</v>
@@ -2010,369 +2010,369 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>Rainwaker</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.0434</v>
+        <v>2.4994</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8558</v>
+        <v>1.0468</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4041</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>2.0434</v>
+        <v>2.4994</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0434</v>
+        <v>2.4994</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.0434</v>
+        <v>2.4994</v>
       </c>
       <c r="I35" t="n">
-        <v>2.0434</v>
+        <v>2.4994</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.0434</v>
+        <v>2.4994</v>
       </c>
       <c r="N35" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.9708</v>
+        <v>2.4631</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8254</v>
+        <v>1.0316</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3748</v>
+        <v>0.5374</v>
       </c>
       <c r="E36" t="n">
-        <v>1.9708</v>
+        <v>2.4631</v>
       </c>
       <c r="F36" t="n">
-        <v>2.2741</v>
+        <v>3.4631</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3033</v>
+        <v>-1</v>
       </c>
       <c r="H36" t="n">
-        <v>2.2741</v>
+        <v>3.4631</v>
       </c>
       <c r="I36" t="n">
-        <v>2.3167</v>
+        <v>2.807</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3033</v>
+        <v>-1</v>
       </c>
       <c r="K36" t="n">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="L36" t="n">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="M36" t="n">
-        <v>2.0134</v>
+        <v>1.807</v>
       </c>
       <c r="N36" t="n">
-        <v>378</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>dennyslaw</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.9558</v>
+        <v>2.3681</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8192</v>
+        <v>0.9918</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3687</v>
+        <v>0.4995</v>
       </c>
       <c r="E37" t="n">
-        <v>1.9558</v>
+        <v>2.3681</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3985</v>
+        <v>2.3681</v>
       </c>
       <c r="G37" t="n">
-        <v>1.5573</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3985</v>
+        <v>2.3681</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4022</v>
+        <v>2.3681</v>
       </c>
       <c r="J37" t="n">
-        <v>1.5573</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="L37" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.9595</v>
+        <v>2.3681</v>
       </c>
       <c r="N37" t="n">
-        <v>374</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.9128</v>
+        <v>2.3594</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8011</v>
+        <v>0.9882</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3514</v>
+        <v>0.4961</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9128</v>
+        <v>2.3594</v>
       </c>
       <c r="F38" t="n">
-        <v>2.9128</v>
+        <v>1.4139</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>0.9455</v>
       </c>
       <c r="H38" t="n">
-        <v>2.9128</v>
+        <v>1.4139</v>
       </c>
       <c r="I38" t="n">
-        <v>2.3609</v>
+        <v>1.4377</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>0.9455</v>
       </c>
       <c r="K38" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L38" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3609</v>
+        <v>2.3832</v>
       </c>
       <c r="N38" t="n">
-        <v>246</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.8322</v>
+        <v>2.3048</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7674</v>
+        <v>0.9653</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3188</v>
+        <v>0.4743</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8322</v>
+        <v>2.3048</v>
       </c>
       <c r="F39" t="n">
-        <v>2.8322</v>
+        <v>2.2558</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>0.049</v>
       </c>
       <c r="H39" t="n">
-        <v>2.8322</v>
+        <v>2.2558</v>
       </c>
       <c r="I39" t="n">
-        <v>2.2956</v>
+        <v>1.8284</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>0.049</v>
       </c>
       <c r="K39" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L39" t="n">
         <v>61</v>
       </c>
       <c r="M39" t="n">
-        <v>1.2956</v>
+        <v>1.8774</v>
       </c>
       <c r="N39" t="n">
-        <v>245</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dennyslaw</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.8211</v>
+        <v>2.2719</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7627</v>
+        <v>0.9515</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3143</v>
+        <v>0.4612</v>
       </c>
       <c r="E40" t="n">
-        <v>1.8211</v>
+        <v>2.2719</v>
       </c>
       <c r="F40" t="n">
-        <v>1.8211</v>
+        <v>2.2719</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.8211</v>
+        <v>2.2719</v>
       </c>
       <c r="I40" t="n">
-        <v>1.8211</v>
+        <v>2.2719</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.8211</v>
+        <v>2.2719</v>
       </c>
       <c r="N40" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.8172</v>
+        <v>2.2604</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7611</v>
+        <v>0.9467</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3127</v>
+        <v>0.4566</v>
       </c>
       <c r="E41" t="n">
-        <v>1.8172</v>
+        <v>2.2604</v>
       </c>
       <c r="F41" t="n">
-        <v>1.7682</v>
+        <v>3.4048</v>
       </c>
       <c r="G41" t="n">
-        <v>0.049</v>
+        <v>-1.1444</v>
       </c>
       <c r="H41" t="n">
-        <v>1.7682</v>
+        <v>3.4048</v>
       </c>
       <c r="I41" t="n">
-        <v>1.4332</v>
+        <v>3.5209</v>
       </c>
       <c r="J41" t="n">
-        <v>0.049</v>
+        <v>-1.1444</v>
       </c>
       <c r="K41" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="L41" t="n">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="M41" t="n">
-        <v>1.4822</v>
+        <v>2.3765</v>
       </c>
       <c r="N41" t="n">
-        <v>256</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.8028</v>
+        <v>2.1008</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7551</v>
+        <v>0.8799</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3069</v>
+        <v>0.393</v>
       </c>
       <c r="E42" t="n">
-        <v>1.8028</v>
+        <v>2.1008</v>
       </c>
       <c r="F42" t="n">
-        <v>1.8028</v>
+        <v>3.1008</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>1.8028</v>
+        <v>3.1008</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8028</v>
+        <v>2.5133</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K42" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M42" t="n">
-        <v>1.8028</v>
+        <v>1.5133</v>
       </c>
       <c r="N42" t="n">
-        <v>133</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.7223</v>
+        <v>2.0719</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7214</v>
+        <v>0.8678</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2744</v>
+        <v>0.3815</v>
       </c>
       <c r="E43" t="n">
-        <v>1.7223</v>
+        <v>2.0719</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7341</v>
+        <v>1.0837</v>
       </c>
       <c r="G43" t="n">
         <v>0.9882</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7341</v>
+        <v>1.0837</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7376</v>
+        <v>1.0928</v>
       </c>
       <c r="J43" t="n">
         <v>0.9882</v>
@@ -2415,7 +2415,7 @@
         <v>229</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7258</v>
+        <v>2.081</v>
       </c>
       <c r="N43" t="n">
         <v>389</v>
@@ -2424,538 +2424,538 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.5954</v>
+        <v>1.9898</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6682</v>
+        <v>0.8334</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2231</v>
+        <v>0.3488</v>
       </c>
       <c r="E44" t="n">
-        <v>1.5954</v>
+        <v>1.9898</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5615</v>
+        <v>0.4325</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0339</v>
+        <v>1.5573</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5615</v>
+        <v>0.4325</v>
       </c>
       <c r="I44" t="n">
-        <v>1.2656</v>
+        <v>0.4398</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0339</v>
+        <v>1.5573</v>
       </c>
       <c r="K44" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="L44" t="n">
-        <v>61</v>
+        <v>249</v>
       </c>
       <c r="M44" t="n">
-        <v>1.2995</v>
+        <v>1.9971</v>
       </c>
       <c r="N44" t="n">
-        <v>256</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>dream3r</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.3496</v>
+        <v>1.9741</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5653</v>
+        <v>0.8268</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1238</v>
+        <v>0.3426</v>
       </c>
       <c r="E45" t="n">
-        <v>1.3496</v>
+        <v>1.9741</v>
       </c>
       <c r="F45" t="n">
-        <v>2.494</v>
+        <v>2.5421</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.1444</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>2.494</v>
+        <v>2.5421</v>
       </c>
       <c r="I45" t="n">
-        <v>2.5407</v>
+        <v>2.5421</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.1444</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="L45" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M45" t="n">
-        <v>1.3963</v>
+        <v>1.9741</v>
       </c>
       <c r="N45" t="n">
-        <v>348</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dream3r</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.3145</v>
+        <v>1.8823</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5506</v>
+        <v>0.7884</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1097</v>
+        <v>0.306</v>
       </c>
       <c r="E46" t="n">
-        <v>1.3145</v>
+        <v>1.8823</v>
       </c>
       <c r="F46" t="n">
-        <v>1.8825</v>
+        <v>1.8484</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.0339</v>
       </c>
       <c r="H46" t="n">
-        <v>1.8825</v>
+        <v>1.8484</v>
       </c>
       <c r="I46" t="n">
-        <v>1.8825</v>
+        <v>1.4982</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.0339</v>
       </c>
       <c r="K46" t="n">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="L46" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="M46" t="n">
-        <v>1.3145</v>
+        <v>1.5321</v>
       </c>
       <c r="N46" t="n">
-        <v>306</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.3131</v>
+        <v>1.8037</v>
       </c>
       <c r="C47" t="n">
-        <v>0.55</v>
+        <v>0.7554</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1091</v>
+        <v>0.2747</v>
       </c>
       <c r="E47" t="n">
-        <v>1.3131</v>
+        <v>1.8037</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3131</v>
+        <v>1.8037</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.3131</v>
+        <v>1.8037</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3131</v>
+        <v>1.8037</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.3131</v>
+        <v>1.8037</v>
       </c>
       <c r="N47" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.2166</v>
+        <v>1.7161</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.7188</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0701</v>
+        <v>0.2398</v>
       </c>
       <c r="E48" t="n">
-        <v>1.2166</v>
+        <v>1.7161</v>
       </c>
       <c r="F48" t="n">
-        <v>1.2166</v>
+        <v>2.2498</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.5337</v>
       </c>
       <c r="H48" t="n">
-        <v>1.2166</v>
+        <v>2.2498</v>
       </c>
       <c r="I48" t="n">
-        <v>1.2166</v>
+        <v>1.8235</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.5337</v>
       </c>
       <c r="K48" t="n">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M48" t="n">
-        <v>1.2166</v>
+        <v>1.2898</v>
       </c>
       <c r="N48" t="n">
-        <v>133</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.1929</v>
+        <v>1.6796</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4996</v>
+        <v>0.7035</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0605</v>
+        <v>0.2252</v>
       </c>
       <c r="E49" t="n">
-        <v>1.1929</v>
+        <v>1.6796</v>
       </c>
       <c r="F49" t="n">
-        <v>1.1929</v>
+        <v>1.6796</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.1929</v>
+        <v>1.6796</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1929</v>
+        <v>1.6796</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1929</v>
+        <v>1.6796</v>
       </c>
       <c r="N49" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.1825</v>
+        <v>1.4878</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4953</v>
+        <v>0.6231</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0563</v>
+        <v>0.1488</v>
       </c>
       <c r="E50" t="n">
-        <v>1.1825</v>
+        <v>1.4878</v>
       </c>
       <c r="F50" t="n">
-        <v>1.7162</v>
+        <v>1.4878</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.5337</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.7162</v>
+        <v>1.4878</v>
       </c>
       <c r="I50" t="n">
-        <v>1.391</v>
+        <v>1.4878</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.5337</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>195</v>
+        <v>123</v>
       </c>
       <c r="L50" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8573000000000001</v>
+        <v>1.4878</v>
       </c>
       <c r="N50" t="n">
-        <v>256</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.1093</v>
+        <v>1.313</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4646</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0268</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>1.1093</v>
+        <v>1.313</v>
       </c>
       <c r="F51" t="n">
-        <v>1.1093</v>
+        <v>1.313</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.1093</v>
+        <v>1.313</v>
       </c>
       <c r="I51" t="n">
-        <v>1.1093</v>
+        <v>1.313</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.1093</v>
+        <v>1.313</v>
       </c>
       <c r="N51" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>zehN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.1002</v>
+        <v>1.3098</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4608</v>
+        <v>0.5486</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0231</v>
+        <v>0.0779</v>
       </c>
       <c r="E52" t="n">
-        <v>1.1002</v>
+        <v>1.3098</v>
       </c>
       <c r="F52" t="n">
-        <v>1.6386</v>
+        <v>1.3098</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.5384</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.6386</v>
+        <v>1.3098</v>
       </c>
       <c r="I52" t="n">
-        <v>1.6539</v>
+        <v>1.3098</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.5384</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>208</v>
+        <v>151</v>
       </c>
       <c r="L52" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1155</v>
+        <v>1.3098</v>
       </c>
       <c r="N52" t="n">
-        <v>341</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.0228</v>
+        <v>1.2025</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4284</v>
+        <v>0.5036</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0352</v>
       </c>
       <c r="E53" t="n">
-        <v>1.0228</v>
+        <v>1.2025</v>
       </c>
       <c r="F53" t="n">
-        <v>1.0228</v>
+        <v>1.7409</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.5384</v>
       </c>
       <c r="H53" t="n">
-        <v>1.0228</v>
+        <v>1.7409</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0228</v>
+        <v>1.7703</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.5384</v>
       </c>
       <c r="K53" t="n">
-        <v>135</v>
+        <v>208</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M53" t="n">
-        <v>1.0228</v>
+        <v>1.2319</v>
       </c>
       <c r="N53" t="n">
-        <v>135</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9912</v>
+        <v>1.1929</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4151</v>
+        <v>0.4996</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0209</v>
+        <v>0.0313</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9912</v>
+        <v>1.1929</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9912</v>
+        <v>1.1929</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9912</v>
+        <v>1.1929</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9912</v>
+        <v>1.1929</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.9912</v>
+        <v>1.1929</v>
       </c>
       <c r="N54" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9113</v>
+        <v>1.1763</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3817</v>
+        <v>0.4927</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.0532</v>
+        <v>0.0247</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9113</v>
+        <v>1.1763</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9113</v>
+        <v>1.1763</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9113</v>
+        <v>1.1763</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9113</v>
+        <v>1.1763</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.9113</v>
+        <v>1.1763</v>
       </c>
       <c r="N55" t="n">
         <v>151</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8047</v>
+        <v>1.1295</v>
       </c>
       <c r="C56" t="n">
-        <v>0.337</v>
+        <v>0.4731</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0963</v>
+        <v>0.0061</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8047</v>
+        <v>1.1295</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2481</v>
+        <v>0.5729</v>
       </c>
       <c r="G56" t="n">
         <v>0.5566</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2481</v>
+        <v>0.5729</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2505</v>
+        <v>0.5826</v>
       </c>
       <c r="J56" t="n">
         <v>0.5566</v>
@@ -3013,7 +3013,7 @@
         <v>94</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8070999999999999</v>
+        <v>1.1392</v>
       </c>
       <c r="N56" t="n">
         <v>273</v>
@@ -3022,78 +3022,78 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>zehN</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7617</v>
+        <v>1.1093</v>
       </c>
       <c r="C57" t="n">
-        <v>0.319</v>
+        <v>0.4646</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.1137</v>
+        <v>-0.002</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7617</v>
+        <v>1.1093</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7617</v>
+        <v>1.1093</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7617</v>
+        <v>1.1093</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7617</v>
+        <v>1.1093</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7617</v>
+        <v>1.1093</v>
       </c>
       <c r="N57" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6952</v>
+        <v>1.0726</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2912</v>
+        <v>0.4492</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1405</v>
+        <v>-0.0166</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6952</v>
+        <v>1.0726</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6952</v>
+        <v>1.0726</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6952</v>
+        <v>1.0726</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6952</v>
+        <v>1.0726</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6952</v>
+        <v>1.0726</v>
       </c>
       <c r="N58" t="n">
         <v>151</v>
@@ -3114,277 +3114,277 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6697</v>
+        <v>1.0228</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2805</v>
+        <v>0.4284</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1508</v>
+        <v>-0.0364</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6697</v>
+        <v>1.0228</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6697</v>
+        <v>1.0228</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6697</v>
+        <v>1.0228</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6697</v>
+        <v>1.0228</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.6697</v>
+        <v>1.0228</v>
       </c>
       <c r="N59" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5963000000000001</v>
+        <v>1.0118</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2497</v>
+        <v>0.4238</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.1805</v>
+        <v>-0.0408</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5963000000000001</v>
+        <v>1.0118</v>
       </c>
       <c r="F60" t="n">
-        <v>1.7359</v>
+        <v>1.0118</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.1396</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.7359</v>
+        <v>1.0118</v>
       </c>
       <c r="I60" t="n">
-        <v>1.7521</v>
+        <v>1.0118</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.1396</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="L60" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.6125</v>
+        <v>1.0118</v>
       </c>
       <c r="N60" t="n">
-        <v>374</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5674</v>
+        <v>0.9943</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2376</v>
+        <v>0.4164</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.1921</v>
+        <v>-0.0478</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5674</v>
+        <v>0.9943</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5674</v>
+        <v>2.1339</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-1.1396</v>
       </c>
       <c r="H61" t="n">
-        <v>0.5674</v>
+        <v>2.1339</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5674</v>
+        <v>2.17</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-1.1396</v>
       </c>
       <c r="K61" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5674</v>
+        <v>1.0304</v>
       </c>
       <c r="N61" t="n">
-        <v>123</v>
+        <v>374</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>poizon</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5084</v>
+        <v>0.9912</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2129</v>
+        <v>0.4151</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.216</v>
+        <v>-0.049</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5084</v>
+        <v>0.9912</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5084</v>
+        <v>0.9912</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5084</v>
+        <v>0.9912</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5084</v>
+        <v>0.9912</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.5084</v>
+        <v>0.9912</v>
       </c>
       <c r="N62" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>REDSTAR</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4842</v>
+        <v>0.78</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2028</v>
+        <v>0.3267</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.2258</v>
+        <v>-0.1332</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4842</v>
+        <v>0.78</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2214</v>
+        <v>1.5541</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2628</v>
+        <v>-0.7741</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2214</v>
+        <v>1.5541</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2224</v>
+        <v>1.5541</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2628</v>
+        <v>-0.7741</v>
       </c>
       <c r="K63" t="n">
-        <v>164</v>
+        <v>209</v>
       </c>
       <c r="L63" t="n">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="M63" t="n">
-        <v>0.4852</v>
+        <v>0.78</v>
       </c>
       <c r="N63" t="n">
-        <v>286</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>HEAP</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4821</v>
+        <v>0.7307</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2019</v>
+        <v>0.306</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.2266</v>
+        <v>-0.1528</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4821</v>
+        <v>0.7307</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.9517</v>
+        <v>0.7307</v>
       </c>
       <c r="G64" t="n">
-        <v>1.4338</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.9517</v>
+        <v>0.7307</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7714</v>
+        <v>0.7307</v>
       </c>
       <c r="J64" t="n">
-        <v>1.4338</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="L64" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.6624</v>
+        <v>0.7307</v>
       </c>
       <c r="N64" t="n">
-        <v>245</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4157</v>
+        <v>0.7057</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1741</v>
+        <v>0.2956</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.2534</v>
+        <v>-0.1628</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4157</v>
+        <v>0.7057</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4157</v>
+        <v>0.7057</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4157</v>
+        <v>0.7057</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4157</v>
+        <v>0.7057</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.4157</v>
+        <v>0.7057</v>
       </c>
       <c r="N65" t="n">
         <v>133</v>
@@ -3436,216 +3436,216 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HEAP</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3994</v>
+        <v>0.5849</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1673</v>
+        <v>0.245</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.26</v>
+        <v>-0.2109</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3994</v>
+        <v>0.5849</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3994</v>
+        <v>0.8859</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-0.301</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3994</v>
+        <v>0.8859</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3994</v>
+        <v>0.9009</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-0.301</v>
       </c>
       <c r="K66" t="n">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3994</v>
+        <v>0.5999000000000001</v>
       </c>
       <c r="N66" t="n">
-        <v>133</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>dav1g</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3485</v>
+        <v>0.5518</v>
       </c>
       <c r="C67" t="n">
-        <v>0.146</v>
+        <v>0.2311</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.2806</v>
+        <v>-0.2241</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3485</v>
+        <v>0.5518</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2863</v>
+        <v>0.9886</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6348</v>
+        <v>-0.4368</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.2863</v>
+        <v>0.9886</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2876</v>
+        <v>1.0223</v>
       </c>
       <c r="J67" t="n">
-        <v>0.6348</v>
+        <v>-0.4368</v>
       </c>
       <c r="K67" t="n">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="L67" t="n">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="M67" t="n">
-        <v>0.3472</v>
+        <v>0.5854999999999999</v>
       </c>
       <c r="N67" t="n">
-        <v>389</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.3182</v>
+        <v>0.5325</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1333</v>
+        <v>0.223</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2928</v>
+        <v>-0.2318</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3182</v>
+        <v>0.5325</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.1023</v>
       </c>
       <c r="G68" t="n">
-        <v>1.2945</v>
+        <v>0.6348</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.1023</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7913</v>
+        <v>-0.1032</v>
       </c>
       <c r="J68" t="n">
-        <v>1.2945</v>
+        <v>0.6348</v>
       </c>
       <c r="K68" t="n">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="L68" t="n">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5032</v>
+        <v>0.5316000000000001</v>
       </c>
       <c r="N68" t="n">
-        <v>245</v>
+        <v>389</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3002</v>
+        <v>0.5232</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1257</v>
+        <v>0.2191</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.3001</v>
+        <v>-0.2355</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3002</v>
+        <v>0.5232</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3002</v>
+        <v>-0.9106</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1.4338</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3002</v>
+        <v>-0.9106</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3002</v>
+        <v>-0.7381</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1.4338</v>
       </c>
       <c r="K69" t="n">
-        <v>123</v>
+        <v>184</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M69" t="n">
-        <v>0.3002</v>
+        <v>0.6957</v>
       </c>
       <c r="N69" t="n">
-        <v>123</v>
+        <v>245</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>poizon</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.1397</v>
+        <v>0.5084</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0585</v>
+        <v>0.2129</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.3649</v>
+        <v>-0.2414</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1397</v>
+        <v>0.5084</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1397</v>
+        <v>0.5084</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1397</v>
+        <v>0.5084</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1397</v>
+        <v>0.5084</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0.1397</v>
+        <v>0.5084</v>
       </c>
       <c r="N70" t="n">
         <v>133</v>
@@ -3666,587 +3666,587 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>REDSTAR</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.1203</v>
+        <v>0.4877</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0504</v>
+        <v>0.2043</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.3728</v>
+        <v>-0.2496</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1203</v>
+        <v>0.4877</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8944</v>
+        <v>0.5387</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.7741</v>
+        <v>-0.051</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8944</v>
+        <v>0.5387</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8944</v>
+        <v>0.4366</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.7741</v>
+        <v>-0.051</v>
       </c>
       <c r="K71" t="n">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="L71" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="M71" t="n">
-        <v>0.1203</v>
+        <v>0.3856</v>
       </c>
       <c r="N71" t="n">
-        <v>306</v>
+        <v>256</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0438</v>
+        <v>0.4833</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0183</v>
+        <v>0.2024</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.4037</v>
+        <v>-0.2514</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0438</v>
+        <v>0.4833</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0948</v>
+        <v>0.2205</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.051</v>
+        <v>0.2628</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0948</v>
+        <v>0.2205</v>
       </c>
       <c r="I72" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.2224</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.051</v>
+        <v>0.2628</v>
       </c>
       <c r="K72" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="L72" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="M72" t="n">
-        <v>0.0258</v>
+        <v>0.4852</v>
       </c>
       <c r="N72" t="n">
-        <v>256</v>
+        <v>286</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dav1g</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.0275</v>
+        <v>0.4433</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.0115</v>
+        <v>0.1857</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.4325</v>
+        <v>-0.2673</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.0275</v>
+        <v>0.4433</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4093</v>
+        <v>0.4433</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.4368</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.4093</v>
+        <v>0.4433</v>
       </c>
       <c r="I73" t="n">
-        <v>0.417</v>
+        <v>0.4433</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.4368</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>232</v>
+        <v>123</v>
       </c>
       <c r="L73" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.01980000000000004</v>
+        <v>0.4433</v>
       </c>
       <c r="N73" t="n">
-        <v>378</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.0814</v>
+        <v>0.3779</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.0341</v>
+        <v>0.1583</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.4542</v>
+        <v>-0.2934</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.0814</v>
+        <v>0.3779</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.0814</v>
+        <v>-0.9166</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1.2945</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.0814</v>
+        <v>-0.9166</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0814</v>
+        <v>-0.7429</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1.2945</v>
       </c>
       <c r="K74" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.0814</v>
+        <v>0.5516</v>
       </c>
       <c r="N74" t="n">
-        <v>152</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.1548</v>
+        <v>0.1789</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.0648</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.4839</v>
+        <v>-0.3726</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.1548</v>
+        <v>0.1789</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.1548</v>
+        <v>1.1789</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.1548</v>
+        <v>1.1789</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1548</v>
+        <v>0.9555</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K75" t="n">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.1548</v>
+        <v>-0.04449999999999998</v>
       </c>
       <c r="N75" t="n">
-        <v>127</v>
+        <v>279</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1966</v>
+        <v>0.1629</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.0823</v>
+        <v>0.0682</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.5008</v>
+        <v>-0.379</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.1966</v>
+        <v>0.1629</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1966</v>
+        <v>0.1629</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.1966</v>
+        <v>0.1629</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1966</v>
+        <v>0.1629</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.1966</v>
+        <v>0.1629</v>
       </c>
       <c r="N76" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>SHOCK</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.2752</v>
+        <v>0.0243</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1153</v>
+        <v>0.0102</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.5325</v>
+        <v>-0.4342</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.2752</v>
+        <v>0.0243</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0258</v>
+        <v>0.0243</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.301</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0258</v>
+        <v>0.0243</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0261</v>
+        <v>0.0243</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.301</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="L77" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.2749</v>
+        <v>0.0243</v>
       </c>
       <c r="N77" t="n">
-        <v>273</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.3486</v>
+        <v>-0.1548</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.146</v>
+        <v>-0.0648</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.5622</v>
+        <v>-0.5056</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.3486</v>
+        <v>-0.1548</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.3486</v>
+        <v>-0.1548</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.3486</v>
+        <v>-0.1548</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3486</v>
+        <v>-0.1548</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.3486</v>
+        <v>-0.1548</v>
       </c>
       <c r="N78" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SHOCK</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.3541</v>
+        <v>-0.1966</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.1483</v>
+        <v>-0.0823</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.5644</v>
+        <v>-0.5222</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.3541</v>
+        <v>-0.1966</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.3541</v>
+        <v>-0.1966</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.3541</v>
+        <v>-0.1966</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3541</v>
+        <v>-0.1966</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.3541</v>
+        <v>-0.1966</v>
       </c>
       <c r="N79" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>SHiPZ</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.3691</v>
+        <v>-0.2312</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1546</v>
+        <v>-0.0968</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.5705</v>
+        <v>-0.536</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.3691</v>
+        <v>-0.2312</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.0291</v>
+        <v>-0.2312</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.0291</v>
+        <v>-0.2312</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0236</v>
+        <v>-0.2312</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="L80" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.3636</v>
+        <v>-0.2312</v>
       </c>
       <c r="N80" t="n">
-        <v>279</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KalubeR</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.3905</v>
+        <v>-0.2319</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1636</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5363</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.3905</v>
+        <v>-0.2319</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.3905</v>
+        <v>0.9198</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>-1.1517</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.3905</v>
+        <v>0.9198</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3905</v>
+        <v>0.9512</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>-1.1517</v>
       </c>
       <c r="K81" t="n">
-        <v>159</v>
+        <v>320</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M81" t="n">
-        <v>-0.3905</v>
+        <v>-0.2004999999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>159</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>bobeksde</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.4224</v>
+        <v>-0.3486</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.1769</v>
+        <v>-0.146</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.592</v>
+        <v>-0.5828</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.4224</v>
+        <v>-0.3486</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.4224</v>
+        <v>-0.3486</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.4224</v>
+        <v>-0.3486</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.4224</v>
+        <v>-0.3486</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.4224</v>
+        <v>-0.3486</v>
       </c>
       <c r="N82" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.4297</v>
+        <v>-0.3691</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.18</v>
+        <v>-0.1546</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.595</v>
+        <v>-0.591</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.4297</v>
+        <v>-0.3691</v>
       </c>
       <c r="F83" t="n">
-        <v>0.5703</v>
+        <v>-0.0291</v>
       </c>
       <c r="G83" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="H83" t="n">
-        <v>0.5703</v>
+        <v>-0.0291</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4623</v>
+        <v>-0.0236</v>
       </c>
       <c r="J83" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="K83" t="n">
         <v>203</v>
@@ -4255,7 +4255,7 @@
         <v>76</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.5377000000000001</v>
+        <v>-0.3636</v>
       </c>
       <c r="N83" t="n">
         <v>279</v>
@@ -4264,860 +4264,860 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>KalubeR</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.43</v>
+        <v>-0.3905</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.1801</v>
+        <v>-0.1636</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.5951</v>
+        <v>-0.5995</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.43</v>
+        <v>-0.3905</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.43</v>
+        <v>-0.3905</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.43</v>
+        <v>-0.3905</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.43</v>
+        <v>-0.3905</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>-0.43</v>
+        <v>-0.3905</v>
       </c>
       <c r="N84" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>bobeksde</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.4932</v>
+        <v>-0.4224</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.2066</v>
+        <v>-0.1769</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.6206</v>
+        <v>-0.6122</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.4932</v>
+        <v>-0.4224</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.4932</v>
+        <v>-0.4224</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.4932</v>
+        <v>-0.4224</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4932</v>
+        <v>-0.4224</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.4932</v>
+        <v>-0.4224</v>
       </c>
       <c r="N85" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SHiPZ</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.6198</v>
+        <v>-0.43</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.2596</v>
+        <v>-0.1801</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.6717</v>
+        <v>-0.6152</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.6198</v>
+        <v>-0.43</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.6198</v>
+        <v>-0.43</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.6198</v>
+        <v>-0.43</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6198</v>
+        <v>-0.43</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.6198</v>
+        <v>-0.43</v>
       </c>
       <c r="N86" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>zen</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.6632</v>
+        <v>-0.4932</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.2778</v>
+        <v>-0.2066</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.6893</v>
+        <v>-0.6404</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.6632</v>
+        <v>-0.4932</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.6632</v>
+        <v>-0.4932</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.6632</v>
+        <v>-0.4932</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.6632</v>
+        <v>-0.4932</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.6632</v>
+        <v>-0.4932</v>
       </c>
       <c r="N87" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.7034</v>
+        <v>-0.5289</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.2946</v>
+        <v>-0.2215</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.7055</v>
+        <v>-0.6546</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7034</v>
+        <v>-0.5289</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.7034</v>
+        <v>-0.5289</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.7034</v>
+        <v>-0.5289</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.7034</v>
+        <v>-0.5289</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.7034</v>
+        <v>-0.5289</v>
       </c>
       <c r="N88" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kressy</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.7602</v>
+        <v>-0.6427</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.3184</v>
+        <v>-0.2692</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.7285</v>
+        <v>-0.7</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.7602</v>
+        <v>-0.6427</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.7602</v>
+        <v>-0.6427</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.7602</v>
+        <v>-0.6427</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.7602</v>
+        <v>-0.6427</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7602</v>
+        <v>-0.6427</v>
       </c>
       <c r="N89" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jackinho</t>
+          <t>zen</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.7938</v>
+        <v>-0.6632</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.3325</v>
+        <v>-0.2778</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.742</v>
+        <v>-0.7081</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.7938</v>
+        <v>-0.6632</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.7938</v>
+        <v>-0.6632</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.7938</v>
+        <v>-0.6632</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7938</v>
+        <v>-0.6632</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>-0.7938</v>
+        <v>-0.6632</v>
       </c>
       <c r="N90" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>kressy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.8249</v>
+        <v>-0.7602</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.3455</v>
+        <v>-0.3184</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.7546</v>
+        <v>-0.7468</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.8249</v>
+        <v>-0.7602</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3268</v>
+        <v>-0.7602</v>
       </c>
       <c r="G91" t="n">
-        <v>-1.1517</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.3268</v>
+        <v>-0.7602</v>
       </c>
       <c r="I91" t="n">
-        <v>0.333</v>
+        <v>-0.7602</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.1517</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>320</v>
+        <v>135</v>
       </c>
       <c r="L91" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.8187</v>
+        <v>-0.7602</v>
       </c>
       <c r="N91" t="n">
-        <v>414</v>
+        <v>135</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>Jackinho</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.962</v>
+        <v>-0.7938</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.4029</v>
+        <v>-0.3325</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.7602</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.962</v>
+        <v>-0.7938</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.962</v>
+        <v>-0.7938</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.962</v>
+        <v>-0.7938</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.962</v>
+        <v>-0.7938</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.962</v>
+        <v>-0.7938</v>
       </c>
       <c r="N92" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>hype</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-1.0312</v>
+        <v>-0.962</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.4319</v>
+        <v>-0.4029</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.8379</v>
+        <v>-0.8272</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.0312</v>
+        <v>-0.962</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.0312</v>
+        <v>-0.962</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-1.0312</v>
+        <v>-0.962</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.0312</v>
+        <v>-0.962</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>-1.0312</v>
+        <v>-0.962</v>
       </c>
       <c r="N93" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DeathZz</t>
+          <t>Farlig</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-1.0357</v>
+        <v>-0.9901</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.4338</v>
+        <v>-0.4147</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.8398</v>
+        <v>-0.8384</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.0357</v>
+        <v>-0.9901</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.2329</v>
+        <v>-0.9901</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1972</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-1.2329</v>
+        <v>-0.9901</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.256</v>
+        <v>-0.9901</v>
       </c>
       <c r="J94" t="n">
-        <v>0.1972</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>232</v>
+        <v>151</v>
       </c>
       <c r="L94" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>-1.0588</v>
+        <v>-0.9901</v>
       </c>
       <c r="N94" t="n">
-        <v>378</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Farlig</t>
+          <t>DeathZz</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-1.1295</v>
+        <v>-1.0174</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.4731</v>
+        <v>-0.4261</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.8777</v>
+        <v>-0.8492</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.1295</v>
+        <v>-1.0174</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.1295</v>
+        <v>-1.2146</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>0.1972</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.1295</v>
+        <v>-1.2146</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.1295</v>
+        <v>-1.256</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>0.1972</v>
       </c>
       <c r="K95" t="n">
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="M95" t="n">
-        <v>-1.1295</v>
+        <v>-1.0588</v>
       </c>
       <c r="N95" t="n">
-        <v>151</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>hype</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-1.1352</v>
+        <v>-1.0312</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.4755</v>
+        <v>-0.4319</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.88</v>
+        <v>-0.8547</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.1352</v>
+        <v>-1.0312</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.1352</v>
+        <v>-1.0312</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>-1.1352</v>
+        <v>-1.0312</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.1352</v>
+        <v>-1.0312</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>-1.1352</v>
+        <v>-1.0312</v>
       </c>
       <c r="N96" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-1.155</v>
+        <v>-1.1352</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.4838</v>
+        <v>-0.4755</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.888</v>
+        <v>-0.8962</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.155</v>
+        <v>-1.1352</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.155</v>
+        <v>-1.1352</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>-1.155</v>
+        <v>-1.1352</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.155</v>
+        <v>-1.1352</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>-1.155</v>
+        <v>-1.1352</v>
       </c>
       <c r="N97" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-1.315</v>
+        <v>-1.2976</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.5508</v>
+        <v>-0.5435</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.9526</v>
+        <v>-0.9609</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.315</v>
+        <v>-1.2976</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.315</v>
+        <v>-0.0895</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>-1.2081</v>
       </c>
       <c r="H98" t="n">
-        <v>-1.315</v>
+        <v>-0.0895</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.315</v>
+        <v>-0.0926</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>-1.2081</v>
       </c>
       <c r="K98" t="n">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="M98" t="n">
-        <v>-1.315</v>
+        <v>-1.3007</v>
       </c>
       <c r="N98" t="n">
-        <v>137</v>
+        <v>348</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>raalz</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.372</v>
+        <v>-1.315</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.5746</v>
+        <v>-0.5508</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.9756</v>
+        <v>-0.9678</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.372</v>
+        <v>-1.315</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.372</v>
+        <v>-1.315</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.372</v>
+        <v>-1.315</v>
       </c>
       <c r="I99" t="n">
-        <v>-1.372</v>
+        <v>-1.315</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>-1.372</v>
+        <v>-1.315</v>
       </c>
       <c r="N99" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MiGHTYMAX</t>
+          <t>raalz</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-1.4378</v>
+        <v>-1.372</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.6022</v>
+        <v>-0.5746</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.0022</v>
+        <v>-0.9905</v>
       </c>
       <c r="E100" t="n">
-        <v>-1.4378</v>
+        <v>-1.372</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.4378</v>
+        <v>-1.372</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>-1.4378</v>
+        <v>-1.372</v>
       </c>
       <c r="I100" t="n">
-        <v>-1.4378</v>
+        <v>-1.372</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>-1.4378</v>
+        <v>-1.372</v>
       </c>
       <c r="N100" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>ZEDKO</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-1.4836</v>
+        <v>-1.3753</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.6214</v>
+        <v>-0.576</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.0207</v>
+        <v>-0.9918</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.4836</v>
+        <v>-1.3753</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.2755</v>
+        <v>-1.3753</v>
       </c>
       <c r="G101" t="n">
-        <v>-1.2081</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.2755</v>
+        <v>-1.3753</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2807</v>
+        <v>-1.3753</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.2081</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>230</v>
+        <v>146</v>
       </c>
       <c r="L101" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>-1.4888</v>
+        <v>-1.3753</v>
       </c>
       <c r="N101" t="n">
-        <v>348</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mirbit</t>
+          <t>MiGHTYMAX</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-1.4896</v>
+        <v>-1.4378</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.6239</v>
+        <v>-0.6022</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.0231</v>
+        <v>-1.0167</v>
       </c>
       <c r="E102" t="n">
-        <v>-1.4896</v>
+        <v>-1.4378</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.4896</v>
+        <v>-1.4378</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.4896</v>
+        <v>-1.4378</v>
       </c>
       <c r="I102" t="n">
-        <v>-1.4896</v>
+        <v>-1.4378</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>-1.4896</v>
+        <v>-1.4378</v>
       </c>
       <c r="N102" t="n">
         <v>127</v>
@@ -5138,691 +5138,691 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>mirbit</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-1.6142</v>
+        <v>-1.4896</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.6761</v>
+        <v>-0.6239</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.0735</v>
+        <v>-1.0374</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.6142</v>
+        <v>-1.4896</v>
       </c>
       <c r="F103" t="n">
-        <v>-1.1555</v>
+        <v>-1.4896</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.4587</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>-1.1555</v>
+        <v>-1.4896</v>
       </c>
       <c r="I103" t="n">
-        <v>-1.1772</v>
+        <v>-1.4896</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.4587</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="L103" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>-1.6359</v>
+        <v>-1.4896</v>
       </c>
       <c r="N103" t="n">
-        <v>348</v>
+        <v>127</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ZEDKO</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-1.6494</v>
+        <v>-1.5013</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.6908</v>
+        <v>-0.6288</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.0877</v>
+        <v>-1.042</v>
       </c>
       <c r="E104" t="n">
-        <v>-1.6494</v>
+        <v>-1.5013</v>
       </c>
       <c r="F104" t="n">
-        <v>-1.6494</v>
+        <v>-1.0426</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>-0.4587</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.6494</v>
+        <v>-1.0426</v>
       </c>
       <c r="I104" t="n">
-        <v>-1.6494</v>
+        <v>-1.0781</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>-0.4587</v>
       </c>
       <c r="K104" t="n">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="M104" t="n">
-        <v>-1.6494</v>
+        <v>-1.5368</v>
       </c>
       <c r="N104" t="n">
-        <v>146</v>
+        <v>348</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Surreal</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-1.652</v>
+        <v>-1.5691</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.6919</v>
+        <v>-0.6572</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.0887</v>
+        <v>-1.069</v>
       </c>
       <c r="E105" t="n">
-        <v>-1.652</v>
+        <v>-1.5691</v>
       </c>
       <c r="F105" t="n">
-        <v>-1.652</v>
+        <v>-1.1842</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>-0.3849</v>
       </c>
       <c r="H105" t="n">
-        <v>-1.652</v>
+        <v>-1.1842</v>
       </c>
       <c r="I105" t="n">
-        <v>-1.652</v>
+        <v>-0.9598</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>-0.3849</v>
       </c>
       <c r="K105" t="n">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M105" t="n">
-        <v>-1.652</v>
+        <v>-1.3447</v>
       </c>
       <c r="N105" t="n">
-        <v>127</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>v1c7oR</t>
+          <t>Surreal</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-1.6889</v>
+        <v>-1.652</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.7074</v>
+        <v>-0.6919</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.1036</v>
+        <v>-1.1021</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.6889</v>
+        <v>-1.652</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.162</v>
+        <v>-1.652</v>
       </c>
       <c r="G106" t="n">
-        <v>-1.5269</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.162</v>
+        <v>-1.652</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.162</v>
+        <v>-1.652</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.5269</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="L106" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>-1.6889</v>
+        <v>-1.652</v>
       </c>
       <c r="N106" t="n">
-        <v>306</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CRUC1AL</t>
+          <t>v1c7oR</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-1.6929</v>
+        <v>-1.6889</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.709</v>
+        <v>-0.7074</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.1053</v>
+        <v>-1.1168</v>
       </c>
       <c r="E107" t="n">
-        <v>-1.6929</v>
+        <v>-1.6889</v>
       </c>
       <c r="F107" t="n">
-        <v>-1.6929</v>
+        <v>-0.162</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>-1.5269</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.6929</v>
+        <v>-0.162</v>
       </c>
       <c r="I107" t="n">
-        <v>-1.6929</v>
+        <v>-0.162</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>-1.5269</v>
       </c>
       <c r="K107" t="n">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M107" t="n">
-        <v>-1.6929</v>
+        <v>-1.6889</v>
       </c>
       <c r="N107" t="n">
-        <v>127</v>
+        <v>306</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FRANSSON</t>
+          <t>CRUC1AL</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-1.9258</v>
+        <v>-1.6929</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.8066</v>
+        <v>-0.709</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.1993</v>
+        <v>-1.1184</v>
       </c>
       <c r="E108" t="n">
-        <v>-1.9258</v>
+        <v>-1.6929</v>
       </c>
       <c r="F108" t="n">
-        <v>-1.9258</v>
+        <v>-1.6929</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-1.9258</v>
+        <v>-1.6929</v>
       </c>
       <c r="I108" t="n">
-        <v>-1.9258</v>
+        <v>-1.6929</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>-1.9258</v>
+        <v>-1.6929</v>
       </c>
       <c r="N108" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>Kyojin</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-1.9498</v>
+        <v>-1.7703</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.8166</v>
+        <v>-0.7415</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.209</v>
+        <v>-1.1492</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.9498</v>
+        <v>-1.7703</v>
       </c>
       <c r="F109" t="n">
-        <v>-1.5649</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.3849</v>
+        <v>-0.8464</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.5649</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.2684</v>
+        <v>-0.9317</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.3849</v>
+        <v>-0.8464</v>
       </c>
       <c r="K109" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L109" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="M109" t="n">
-        <v>-1.6533</v>
+        <v>-1.7781</v>
       </c>
       <c r="N109" t="n">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>FRANSSON</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-1.9531</v>
+        <v>-1.9258</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.8066</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.2104</v>
+        <v>-1.2111</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.9531</v>
+        <v>-1.9258</v>
       </c>
       <c r="F110" t="n">
-        <v>-1.9531</v>
+        <v>-1.9258</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.9531</v>
+        <v>-1.9258</v>
       </c>
       <c r="I110" t="n">
-        <v>-1.9531</v>
+        <v>-1.9258</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-1.9531</v>
+        <v>-1.9258</v>
       </c>
       <c r="N110" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>beastik</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-1.9607</v>
+        <v>-1.9262</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.8212</v>
+        <v>-0.8068</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.2134</v>
+        <v>-1.2113</v>
       </c>
       <c r="E111" t="n">
-        <v>-1.9607</v>
+        <v>-1.9262</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.9607</v>
+        <v>-1.9262</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.9607</v>
+        <v>-1.9262</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.9607</v>
+        <v>-1.9262</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-1.9607</v>
+        <v>-1.9262</v>
       </c>
       <c r="N111" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>sausol</t>
+          <t>Duplicate</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-1.9631</v>
+        <v>-1.9531</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.8222</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.2144</v>
+        <v>-1.222</v>
       </c>
       <c r="E112" t="n">
-        <v>-1.9631</v>
+        <v>-1.9531</v>
       </c>
       <c r="F112" t="n">
-        <v>-1.9631</v>
+        <v>-1.9531</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-1.9631</v>
+        <v>-1.9531</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.9631</v>
+        <v>-1.9531</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>-1.9631</v>
+        <v>-1.9531</v>
       </c>
       <c r="N112" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHiNE</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-1.9814</v>
+        <v>-1.9607</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.8299</v>
+        <v>-0.8212</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.2218</v>
+        <v>-1.2251</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.9814</v>
+        <v>-1.9607</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.9814</v>
+        <v>-1.9607</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.9814</v>
+        <v>-1.9607</v>
       </c>
       <c r="I113" t="n">
-        <v>-1.9814</v>
+        <v>-1.9607</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>-1.9814</v>
+        <v>-1.9607</v>
       </c>
       <c r="N113" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>beastik</t>
+          <t>sausol</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-2.0014</v>
+        <v>-1.9631</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.8383</v>
+        <v>-0.8222</v>
       </c>
       <c r="D114" t="n">
-        <v>-1.2299</v>
+        <v>-1.226</v>
       </c>
       <c r="E114" t="n">
-        <v>-2.0014</v>
+        <v>-1.9631</v>
       </c>
       <c r="F114" t="n">
-        <v>-2.0014</v>
+        <v>-1.9631</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-2.0014</v>
+        <v>-1.9631</v>
       </c>
       <c r="I114" t="n">
-        <v>-2.0014</v>
+        <v>-1.9631</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>-2.0014</v>
+        <v>-1.9631</v>
       </c>
       <c r="N114" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>SHiNE</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-2.4411</v>
+        <v>-1.9814</v>
       </c>
       <c r="C115" t="n">
-        <v>-1.0224</v>
+        <v>-0.8299</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.4075</v>
+        <v>-1.2333</v>
       </c>
       <c r="E115" t="n">
-        <v>-2.4411</v>
+        <v>-1.9814</v>
       </c>
       <c r="F115" t="n">
-        <v>-2.4411</v>
+        <v>-1.9814</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.4411</v>
+        <v>-1.9814</v>
       </c>
       <c r="I115" t="n">
-        <v>-2.4411</v>
+        <v>-1.9814</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-2.4411</v>
+        <v>-1.9814</v>
       </c>
       <c r="N115" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-2.4568</v>
+        <v>-2.4411</v>
       </c>
       <c r="C116" t="n">
-        <v>-1.029</v>
+        <v>-1.0224</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.4139</v>
+        <v>-1.4164</v>
       </c>
       <c r="E116" t="n">
-        <v>-2.4568</v>
+        <v>-2.4411</v>
       </c>
       <c r="F116" t="n">
-        <v>-2.4568</v>
+        <v>-2.4411</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-2.4568</v>
+        <v>-2.4411</v>
       </c>
       <c r="I116" t="n">
-        <v>-2.4568</v>
+        <v>-2.4411</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-2.4568</v>
+        <v>-2.4411</v>
       </c>
       <c r="N116" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kyojin</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-2.5414</v>
+        <v>-2.4568</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.0644</v>
+        <v>-1.029</v>
       </c>
       <c r="D117" t="n">
-        <v>-1.448</v>
+        <v>-1.4227</v>
       </c>
       <c r="E117" t="n">
-        <v>-2.5414</v>
+        <v>-2.4568</v>
       </c>
       <c r="F117" t="n">
-        <v>-1.695</v>
+        <v>-2.4568</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.8464</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-1.695</v>
+        <v>-2.4568</v>
       </c>
       <c r="I117" t="n">
-        <v>-1.7029</v>
+        <v>-2.4568</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.8464</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="L117" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>-2.5493</v>
+        <v>-2.4568</v>
       </c>
       <c r="N117" t="n">
-        <v>286</v>
+        <v>141</v>
       </c>
     </row>
     <row r="118">
@@ -5832,28 +5832,28 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-3.1541</v>
+        <v>-3.0926</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.321</v>
+        <v>-1.2953</v>
       </c>
       <c r="D118" t="n">
-        <v>-1.6955</v>
+        <v>-1.676</v>
       </c>
       <c r="E118" t="n">
-        <v>-3.1541</v>
+        <v>-3.0926</v>
       </c>
       <c r="F118" t="n">
-        <v>-1.1541</v>
+        <v>-1.0926</v>
       </c>
       <c r="G118" t="n">
         <v>-2</v>
       </c>
       <c r="H118" t="n">
-        <v>-1.1541</v>
+        <v>-1.0926</v>
       </c>
       <c r="I118" t="n">
-        <v>-1.1541</v>
+        <v>-1.0926</v>
       </c>
       <c r="J118" t="n">
         <v>-2</v>
@@ -5865,7 +5865,7 @@
         <v>97</v>
       </c>
       <c r="M118" t="n">
-        <v>-3.1541</v>
+        <v>-3.0926</v>
       </c>
       <c r="N118" t="n">
         <v>306</v>
@@ -5884,7 +5884,7 @@
         <v>-1.4374</v>
       </c>
       <c r="D119" t="n">
-        <v>-1.8078</v>
+        <v>-1.8112</v>
       </c>
       <c r="E119" t="n">
         <v>-3.4319</v>
@@ -5930,7 +5930,7 @@
         <v>-1.4779</v>
       </c>
       <c r="D120" t="n">
-        <v>-1.8468</v>
+        <v>-1.8497</v>
       </c>
       <c r="E120" t="n">
         <v>-3.5286</v>
